--- a/daily_nse_scans_alerts/automated_alert_2026-10-07.xlsx
+++ b/daily_nse_scans_alerts/automated_alert_2026-10-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$H$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +77,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,17 +449,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,6 +504,11 @@
           <t>Sideways</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Volume Signal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,6 +541,11 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -543,6 +578,11 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -575,6 +615,11 @@
       <c r="H4" t="b">
         <v>0</v>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -589,23 +634,28 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78.65000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="E5" t="n">
-        <v>89.77</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4116</v>
+        <v>1.2874</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -639,6 +689,11 @@
       <c r="H6" t="b">
         <v>0</v>
       </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -653,23 +708,28 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61.7</v>
+        <v>61.77</v>
       </c>
       <c r="E7" t="n">
-        <v>88.16</v>
+        <v>88.22</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0247</v>
+        <v>0.9427</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -703,6 +763,11 @@
       <c r="H8" t="b">
         <v>0</v>
       </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -735,6 +800,11 @@
       <c r="H9" t="b">
         <v>0</v>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -767,6 +837,11 @@
       <c r="H10" t="b">
         <v>0</v>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -799,48 +874,58 @@
       <c r="H11" t="b">
         <v>0</v>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DPABHUSHAN</t>
+          <t>DPWIRES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>D. P. Abhushan Limited</t>
+          <t>D P Wires Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2174</v>
+        <v>227.46</v>
       </c>
       <c r="E12" t="n">
-        <v>84.16</v>
+        <v>84.63</v>
       </c>
       <c r="F12" t="n">
-        <v>80.61579999999999</v>
+        <v>7.909</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>DPABHUSHAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sun TV Network Limited</t>
+          <t>D. P. Abhushan Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -849,30 +934,35 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>632.1</v>
+        <v>2174</v>
       </c>
       <c r="E13" t="n">
-        <v>83.76000000000001</v>
+        <v>84.16</v>
       </c>
       <c r="F13" t="n">
-        <v>17.4893</v>
+        <v>80.61579999999999</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dynamatic Technologies Limited</t>
+          <t>Sun TV Network Limited</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -881,30 +971,35 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14279</v>
+        <v>632.1</v>
       </c>
       <c r="E14" t="n">
-        <v>83.65000000000001</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>155.9074</v>
+        <v>17.4893</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DPWIRES</t>
+          <t>SPECTRUM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D P Wires Limited</t>
+          <t>Spectrum Electrical Industries Limited</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -913,83 +1008,98 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>221.54</v>
+        <v>3915.9</v>
       </c>
       <c r="E15" t="n">
-        <v>83.55</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>6.2602</v>
+        <v>47.2354</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPECTRUM</t>
+          <t>JAYKAY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spectrum Electrical Industries Limited</t>
+          <t>Jaykay Enterprises Limited</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3915.9</v>
+        <v>263.45</v>
       </c>
       <c r="E16" t="n">
-        <v>83.34999999999999</v>
+        <v>83.14</v>
       </c>
       <c r="F16" t="n">
-        <v>47.2354</v>
+        <v>5.9118</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>SHREEJISPG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Raymond Limited</t>
+          <t>Shreeji Shipping Global Limited</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1294.3</v>
+        <v>802.1</v>
       </c>
       <c r="E17" t="n">
-        <v>83.28</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>6.7091</v>
+        <v>4.5232</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1023,16 +1133,21 @@
       <c r="H18" t="b">
         <v>0</v>
       </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SHREEJISPG</t>
+          <t>KILITCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shreeji Shipping Global Limited</t>
+          <t>Kilitch Drugs (India) Limited</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1041,30 +1156,35 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>796.5</v>
+        <v>260.7</v>
       </c>
       <c r="E19" t="n">
-        <v>82.06999999999999</v>
+        <v>82</v>
       </c>
       <c r="F19" t="n">
-        <v>4.4528</v>
+        <v>4.2649</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KILITCH</t>
+          <t>VALIANTORG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kilitch Drugs (India) Limited</t>
+          <t>Valiant Organics Limited</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1073,30 +1193,35 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>260.7</v>
+        <v>496.8</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>81.37</v>
       </c>
       <c r="F20" t="n">
-        <v>4.2649</v>
+        <v>5.8012</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VALIANTORG</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Valiant Organics Limited</t>
+          <t>Rossell Techsys Limited</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1105,30 +1230,35 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>496.8</v>
+        <v>1612.1</v>
       </c>
       <c r="E21" t="n">
-        <v>81.37</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>5.8012</v>
+        <v>14.0294</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>SHIVAUM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rossell Techsys Limited</t>
+          <t>Shiv Aum Steels Limited</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1137,62 +1267,72 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1612.1</v>
+        <v>552.65</v>
       </c>
       <c r="E22" t="n">
-        <v>80.79000000000001</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>14.0294</v>
+        <v>5.4174</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>MOBIKWIK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SIGMA ADVANCED SYSTEMS LIMITED</t>
+          <t>One Mobikwik Systems Limited</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1119.4</v>
+        <v>256.08</v>
       </c>
       <c r="E23" t="n">
-        <v>80.69</v>
+        <v>80.08</v>
       </c>
       <c r="F23" t="n">
-        <v>18.6413</v>
+        <v>4.8458</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SHIVAUM</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shiv Aum Steels Limited</t>
+          <t>Gretex Corporate Services Limited</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1201,190 +1341,220 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>552.65</v>
+        <v>693.05</v>
       </c>
       <c r="E24" t="n">
-        <v>80.54000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="F24" t="n">
-        <v>5.4174</v>
+        <v>3.0414</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gretex Corporate Services Limited</t>
+          <t>Morepen Laboratories Limited</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>693.05</v>
+        <v>146.97</v>
       </c>
       <c r="E25" t="n">
-        <v>79.75</v>
+        <v>77.73</v>
       </c>
       <c r="F25" t="n">
-        <v>3.0414</v>
+        <v>1.4633</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JAYKAY</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Limited</t>
+          <t>Fine Organic Industries Limited</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>240.02</v>
+        <v>5625.5</v>
       </c>
       <c r="E26" t="n">
-        <v>78.75</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>3.9144</v>
+        <v>44.8811</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DMCC</t>
+          <t>LOKESHMACH</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DMCC SPECIALITY CHEMICALS LIMITED</t>
+          <t>Lokesh Machines Limited</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>355.8</v>
+        <v>465.45</v>
       </c>
       <c r="E27" t="n">
-        <v>76.93000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>5.3012</v>
+        <v>13.0327</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KINGFA</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kingfa Science &amp; Technology (India) Limited</t>
+          <t>Aequs Limited</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6932</v>
+        <v>288.15</v>
       </c>
       <c r="E28" t="n">
-        <v>76.84999999999999</v>
+        <v>77.53</v>
       </c>
       <c r="F28" t="n">
-        <v>56.4848</v>
+        <v>4.9416</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>DMCC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aequs Limited</t>
+          <t>DMCC SPECIALITY CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>286.1</v>
+        <v>356.05</v>
       </c>
       <c r="E29" t="n">
-        <v>76.77</v>
+        <v>76.98</v>
       </c>
       <c r="F29" t="n">
-        <v>5.2225</v>
+        <v>6.4245</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>INDOAMIN</t>
+          <t>KINGFA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Indo Amines Limited</t>
+          <t>Kingfa Science &amp; Technology (India) Limited</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1393,30 +1563,35 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>161.16</v>
+        <v>6932</v>
       </c>
       <c r="E30" t="n">
-        <v>76.77</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>2.0812</v>
+        <v>56.4848</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>INDOAMIN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sterlite Technologies Limited</t>
+          <t>Indo Amines Limited</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1425,62 +1600,72 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1016.7</v>
+        <v>161.16</v>
       </c>
       <c r="E31" t="n">
-        <v>76.53</v>
+        <v>76.77</v>
       </c>
       <c r="F31" t="n">
-        <v>11.2255</v>
+        <v>2.0812</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MUKANDLTD</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mukand Limited</t>
+          <t>Sterlite Technologies Limited</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>181.55</v>
+        <v>1016.8</v>
       </c>
       <c r="E32" t="n">
-        <v>76.43000000000001</v>
+        <v>76.53</v>
       </c>
       <c r="F32" t="n">
-        <v>3.2087</v>
+        <v>11.7111</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KRISHNADEF</t>
+          <t>MUKANDLTD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Krishna Defence And Allied Industries Limited</t>
+          <t>Mukand Limited</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1489,94 +1674,109 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1312.3</v>
+        <v>181.55</v>
       </c>
       <c r="E33" t="n">
-        <v>76.41</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>28.509</v>
+        <v>3.2087</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Morepen Laboratories Limited</t>
+          <t>Sunflag Iron And Steel Company Limited</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>143.96</v>
+        <v>474.4</v>
       </c>
       <c r="E34" t="n">
-        <v>76.36</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0093</v>
+        <v>7.986</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MOBIKWIK</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>One Mobikwik Systems Limited</t>
+          <t>Rajoo Engineers Limited</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>242.14</v>
+        <v>62.37</v>
       </c>
       <c r="E35" t="n">
-        <v>76.34999999999999</v>
+        <v>75.77</v>
       </c>
       <c r="F35" t="n">
-        <v>2.3105</v>
+        <v>0.5554</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LOKESHMACH</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lokesh Machines Limited</t>
+          <t>Sri Lotus Developers and Realty Limited</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1585,62 +1785,72 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>455.7</v>
+        <v>244.73</v>
       </c>
       <c r="E36" t="n">
-        <v>75.92</v>
+        <v>75.61</v>
       </c>
       <c r="F36" t="n">
-        <v>11.4358</v>
+        <v>1.5767</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AXISCADES Technologies Limited</t>
+          <t>Cupid Limited</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2288.5</v>
+        <v>343.95</v>
       </c>
       <c r="E37" t="n">
-        <v>75.76000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="F37" t="n">
-        <v>39.2176</v>
+        <v>6.2807</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>EVERESTIND</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sri Lotus Developers and Realty Limited</t>
+          <t>Everest Industries Limited</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1649,30 +1859,35 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>244.73</v>
+        <v>515.95</v>
       </c>
       <c r="E38" t="n">
-        <v>75.61</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5767</v>
+        <v>10.6199</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EVERESTIND</t>
+          <t>OMFREIGHT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Everest Industries Limited</t>
+          <t>Om Freight Forwarders Limited</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1681,94 +1896,109 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>515.95</v>
+        <v>105</v>
       </c>
       <c r="E39" t="n">
-        <v>74.90000000000001</v>
+        <v>74.75</v>
       </c>
       <c r="F39" t="n">
-        <v>10.6199</v>
+        <v>1.7503</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OMFREIGHT</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Om Freight Forwarders Limited</t>
+          <t>SIGMA ADVANCED SYSTEMS LIMITED</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>105</v>
+        <v>1091.6</v>
       </c>
       <c r="E40" t="n">
-        <v>74.75</v>
+        <v>74.55</v>
       </c>
       <c r="F40" t="n">
-        <v>1.7503</v>
+        <v>13.0488</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
       </c>
       <c r="H40" t="b">
         <v>0</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>KAMATHOTEL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ram Ratna Wires Limited</t>
+          <t>Kamat Hotels (I) Limited</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>641.2</v>
+        <v>262.89</v>
       </c>
       <c r="E41" t="n">
-        <v>74.39</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>6.4106</v>
+        <v>1.764</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NINSYS</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NINtec Systems Limited</t>
+          <t>Ram Ratna Wires Limited</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1777,30 +2007,35 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>822.55</v>
+        <v>641.2</v>
       </c>
       <c r="E42" t="n">
-        <v>74.38</v>
+        <v>74.39</v>
       </c>
       <c r="F42" t="n">
-        <v>15.4146</v>
+        <v>6.4106</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>NINSYS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fine Organic Industries Limited</t>
+          <t>NINtec Systems Limited</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1809,51 +2044,61 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5537</v>
+        <v>822.55</v>
       </c>
       <c r="E43" t="n">
-        <v>74.09</v>
+        <v>74.38</v>
       </c>
       <c r="F43" t="n">
-        <v>24.0215</v>
+        <v>15.4146</v>
       </c>
       <c r="G43" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SMCGLOBAL</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SMC Global Securities Limited</t>
+          <t>Cello World Limited</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>110.55</v>
+        <v>390.65</v>
       </c>
       <c r="E44" t="n">
-        <v>74.08</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>2.6423</v>
+        <v>6.6755</v>
       </c>
       <c r="G44" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1887,80 +2132,95 @@
       <c r="H45" t="b">
         <v>0</v>
       </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>SHANTIGOLD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sunflag Iron And Steel Company Limited</t>
+          <t>Shanti Gold International Limited</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>459.05</v>
+        <v>341.05</v>
       </c>
       <c r="E46" t="n">
-        <v>73.67</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>8.069599999999999</v>
+        <v>4.8945</v>
       </c>
       <c r="G46" t="b">
         <v>1</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DEVX</t>
+          <t>SMCGLOBAL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dev Accelerator Limited</t>
+          <t>SMC Global Securities Limited</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>39.62</v>
+        <v>110.24</v>
       </c>
       <c r="E47" t="n">
-        <v>73.43000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4736</v>
+        <v>2.5579</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>DEVX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Unimech Aerospace and Manufacturing Limited</t>
+          <t>Dev Accelerator Limited</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1969,19 +2229,24 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1873.1</v>
+        <v>39.62</v>
       </c>
       <c r="E48" t="n">
-        <v>73.18000000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>14.7868</v>
+        <v>0.4736</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
       </c>
       <c r="H48" t="b">
         <v>0</v>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -2015,16 +2280,21 @@
       <c r="H49" t="b">
         <v>0</v>
       </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optiemus Infracom Limited</t>
+          <t>Eurotex Industries and Exports Limited</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2033,94 +2303,109 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>889.9</v>
+        <v>16.33</v>
       </c>
       <c r="E50" t="n">
-        <v>72.98</v>
+        <v>72.77</v>
       </c>
       <c r="F50" t="n">
-        <v>13.7923</v>
+        <v>0.5305</v>
       </c>
       <c r="G50" t="b">
         <v>1</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KAMATHOTEL</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kamat Hotels (I) Limited</t>
+          <t>Gandhar Oil Refinery (India) Limited</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>258.82</v>
+        <v>299.2</v>
       </c>
       <c r="E51" t="n">
-        <v>72.88</v>
+        <v>72.53</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9851</v>
+        <v>1.66</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>KAVDEFENCE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Eurotex Industries and Exports Limited</t>
+          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16.33</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>72.77</v>
+        <v>72.45</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5305</v>
+        <v>0.4462</v>
       </c>
       <c r="G52" t="b">
         <v>1</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SHANTIGOLD</t>
+          <t>SOMANYCERA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shanti Gold International Limited</t>
+          <t>Somany Ceramics Limited</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2129,30 +2414,35 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>336.65</v>
+        <v>625</v>
       </c>
       <c r="E53" t="n">
-        <v>72.7</v>
+        <v>72.39</v>
       </c>
       <c r="F53" t="n">
-        <v>4.3868</v>
+        <v>0.9604</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
       </c>
       <c r="H53" t="b">
         <v>0</v>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SOMANYCERA</t>
+          <t>SSWL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Somany Ceramics Limited</t>
+          <t>Steel Strips Wheels Limited</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2161,51 +2451,61 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>625</v>
+        <v>424.7</v>
       </c>
       <c r="E54" t="n">
-        <v>72.39</v>
+        <v>72.25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9604</v>
+        <v>2.4313</v>
       </c>
       <c r="G54" t="b">
         <v>1</v>
       </c>
       <c r="H54" t="b">
         <v>0</v>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SSWL</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Steel Strips Wheels Limited</t>
+          <t>Jamna Auto Industries Limited</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>424.7</v>
+        <v>151.77</v>
       </c>
       <c r="E55" t="n">
-        <v>72.25</v>
+        <v>72.23</v>
       </c>
       <c r="F55" t="n">
-        <v>2.4313</v>
+        <v>1.4457</v>
       </c>
       <c r="G55" t="b">
         <v>1</v>
       </c>
       <c r="H55" t="b">
         <v>0</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -2239,48 +2539,58 @@
       <c r="H56" t="b">
         <v>0</v>
       </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ALICON</t>
+          <t>ARIHANTCAP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alicon Castalloy Limited</t>
+          <t>Arihant Capital Markets Limited</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>866.9</v>
+        <v>97.38</v>
       </c>
       <c r="E57" t="n">
-        <v>72.06999999999999</v>
+        <v>72.13</v>
       </c>
       <c r="F57" t="n">
-        <v>15.8651</v>
+        <v>0.5429</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
       </c>
       <c r="H57" t="b">
         <v>0</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PROTEAN</t>
+          <t>ALICON</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Protean eGov Technologies Limited</t>
+          <t>Alicon Castalloy Limited</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2289,94 +2599,109 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>689.25</v>
+        <v>866.9</v>
       </c>
       <c r="E58" t="n">
-        <v>71.70999999999999</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>8.3911</v>
+        <v>15.8651</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
       </c>
       <c r="H58" t="b">
         <v>0</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ABAN</t>
+          <t>ARFIN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Aban Offshore Limited</t>
+          <t>Arfin India Limited</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>16.92</v>
+        <v>103.06</v>
       </c>
       <c r="E59" t="n">
-        <v>71.58</v>
+        <v>71.77</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3514</v>
+        <v>1.0754</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
       </c>
       <c r="H59" t="b">
         <v>0</v>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>HFCL Limited</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>551.55</v>
+        <v>271.9</v>
       </c>
       <c r="E60" t="n">
-        <v>71.23999999999999</v>
+        <v>71.59</v>
       </c>
       <c r="F60" t="n">
-        <v>5.7663</v>
+        <v>5.7943</v>
       </c>
       <c r="G60" t="b">
         <v>1</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DELPHIFX</t>
+          <t>ABAN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DELPHI WORLD MONEY LIMITED</t>
+          <t>Aban Offshore Limited</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2385,62 +2710,72 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7.17</v>
+        <v>16.92</v>
       </c>
       <c r="E61" t="n">
-        <v>71.23999999999999</v>
+        <v>71.58</v>
       </c>
       <c r="F61" t="n">
-        <v>0.219</v>
+        <v>0.3514</v>
       </c>
       <c r="G61" t="b">
         <v>1</v>
       </c>
       <c r="H61" t="b">
         <v>0</v>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DELTACORP</t>
+          <t>TATVA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Delta Corp Limited</t>
+          <t>Tatva Chintan Pharma Chem Limited</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>84.34</v>
+        <v>1991.2</v>
       </c>
       <c r="E62" t="n">
-        <v>71.23</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>2.0192</v>
+        <v>17.9997</v>
       </c>
       <c r="G62" t="b">
         <v>1</v>
       </c>
       <c r="H62" t="b">
         <v>0</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WELSPUNLIV</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Welspun Living Limited</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2449,30 +2784,35 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>237.86</v>
+        <v>551.55</v>
       </c>
       <c r="E63" t="n">
-        <v>71.01000000000001</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4762</v>
+        <v>5.7663</v>
       </c>
       <c r="G63" t="b">
         <v>1</v>
       </c>
       <c r="H63" t="b">
         <v>0</v>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Omnitech Engineering Limited</t>
+          <t>DELPHI WORLD MONEY LIMITED</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2481,94 +2821,109 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>656.95</v>
+        <v>7.17</v>
       </c>
       <c r="E64" t="n">
-        <v>70.97</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>12.208</v>
+        <v>0.219</v>
       </c>
       <c r="G64" t="b">
         <v>1</v>
       </c>
       <c r="H64" t="b">
         <v>0</v>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MMWL</t>
+          <t>PARAGMILK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Media Matrix Worldwide Limited</t>
+          <t>Parag Milk Foods Limited</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>17.14</v>
+        <v>311.8</v>
       </c>
       <c r="E65" t="n">
-        <v>70.87</v>
+        <v>71.16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3739</v>
+        <v>2.9342</v>
       </c>
       <c r="G65" t="b">
         <v>1</v>
       </c>
       <c r="H65" t="b">
         <v>0</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Marine Electricals (India) Limited</t>
+          <t>AXISCADES Technologies Limited</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>478.85</v>
+        <v>2245.6</v>
       </c>
       <c r="E66" t="n">
-        <v>70.73999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>4.3847</v>
+        <v>30.8839</v>
       </c>
       <c r="G66" t="b">
         <v>1</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PARAGMILK</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Parag Milk Foods Limited</t>
+          <t>Omnitech Engineering Limited</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2577,30 +2932,35 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>308.7</v>
+        <v>656.95</v>
       </c>
       <c r="E67" t="n">
-        <v>70.34</v>
+        <v>70.97</v>
       </c>
       <c r="F67" t="n">
-        <v>1.4554</v>
+        <v>12.208</v>
       </c>
       <c r="G67" t="b">
         <v>1</v>
       </c>
       <c r="H67" t="b">
         <v>0</v>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KISSHT</t>
+          <t>MMWL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OnEMI Technology Solutions Limited</t>
+          <t>Media Matrix Worldwide Limited</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2609,158 +2969,183 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>383.1</v>
+        <v>17.14</v>
       </c>
       <c r="E68" t="n">
-        <v>70.27</v>
+        <v>70.87</v>
       </c>
       <c r="F68" t="n">
-        <v>2.3765</v>
+        <v>0.3739</v>
       </c>
       <c r="G68" t="b">
         <v>1</v>
       </c>
       <c r="H68" t="b">
         <v>0</v>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FLEXITUFF</t>
+          <t>DBOL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Flexituff Ventures International Limited</t>
+          <t>Dhampur Bio Organics Limited</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3.13</v>
+        <v>140.25</v>
       </c>
       <c r="E69" t="n">
-        <v>70.2</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1111</v>
+        <v>2.1855</v>
       </c>
       <c r="G69" t="b">
         <v>1</v>
       </c>
       <c r="H69" t="b">
         <v>0</v>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cupid Limited</t>
+          <t>Panama Petrochem Limited</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>324.2</v>
+        <v>537</v>
       </c>
       <c r="E70" t="n">
-        <v>70.12</v>
+        <v>70.8</v>
       </c>
       <c r="F70" t="n">
-        <v>4.9108</v>
+        <v>5.0416</v>
       </c>
       <c r="G70" t="b">
         <v>1</v>
       </c>
       <c r="H70" t="b">
         <v>0</v>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WEWIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WE WIN LIMITED</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>51.92</v>
+        <v>440</v>
       </c>
       <c r="E71" t="n">
-        <v>69.69</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9239000000000001</v>
+        <v>2.2346</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
       </c>
       <c r="H71" t="b">
         <v>0</v>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CUBEXTUB</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cubex Tubings Limited</t>
+          <t>Unimech Aerospace and Manufacturing Limited</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>149.91</v>
+        <v>1854.5</v>
       </c>
       <c r="E72" t="n">
-        <v>69.29000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="F72" t="n">
-        <v>4.8514</v>
+        <v>14.4065</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
       </c>
       <c r="H72" t="b">
         <v>0</v>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>KISSHT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>OnEMI Technology Solutions Limited</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2769,30 +3154,35 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>22.95</v>
+        <v>383.1</v>
       </c>
       <c r="E73" t="n">
-        <v>68.98</v>
+        <v>70.27</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4437</v>
+        <v>2.3765</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
       </c>
       <c r="H73" t="b">
         <v>0</v>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KAVDEFENCE</t>
+          <t>FLEXITUFF</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
+          <t>Flexituff Ventures International Limited</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2801,62 +3191,72 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>85.55</v>
+        <v>3.13</v>
       </c>
       <c r="E74" t="n">
-        <v>68.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0665</v>
+        <v>0.1111</v>
       </c>
       <c r="G74" t="b">
         <v>1</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PANACHE</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Panache Digilife Limited</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>569</v>
+        <v>290.6</v>
       </c>
       <c r="E75" t="n">
-        <v>68.78</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>2.4434</v>
+        <v>3.1427</v>
       </c>
       <c r="G75" t="b">
         <v>1</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>WEWIN</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HFCL Limited</t>
+          <t>WE WIN LIMITED</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2865,94 +3265,109 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>262.78</v>
+        <v>51.92</v>
       </c>
       <c r="E76" t="n">
-        <v>68.76000000000001</v>
+        <v>69.69</v>
       </c>
       <c r="F76" t="n">
-        <v>4.5416</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
       </c>
       <c r="H76" t="b">
         <v>0</v>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DHAMPURSUG</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Limited</t>
+          <t>Marine Electricals (India) Limited</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>188.81</v>
+        <v>476.4</v>
       </c>
       <c r="E77" t="n">
-        <v>68.73</v>
+        <v>69.63</v>
       </c>
       <c r="F77" t="n">
-        <v>1.9004</v>
+        <v>4.8416</v>
       </c>
       <c r="G77" t="b">
         <v>1</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>ZIMLAB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gujarat Kidney And Super Speciality Limited</t>
+          <t>Zim Laboratories Limited</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>193.62</v>
+        <v>146.61</v>
       </c>
       <c r="E78" t="n">
-        <v>68.59</v>
+        <v>69.48</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6725</v>
+        <v>0.1123</v>
       </c>
       <c r="G78" t="b">
         <v>1</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SUNDROP</t>
+          <t>CUBEXTUB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sundrop Brands Limited</t>
+          <t>Cubex Tubings Limited</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2961,62 +3376,72 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>746.8</v>
+        <v>149.91</v>
       </c>
       <c r="E79" t="n">
-        <v>68.59</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>3.6931</v>
+        <v>4.8514</v>
       </c>
       <c r="G79" t="b">
         <v>1</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RPTECH</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rashi Peripherals Limited</t>
+          <t>Leela Palaces Hotels &amp; Resorts Limited</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>958.25</v>
+        <v>602.45</v>
       </c>
       <c r="E80" t="n">
-        <v>68.45</v>
+        <v>69.12</v>
       </c>
       <c r="F80" t="n">
-        <v>12.0136</v>
+        <v>5.0079</v>
       </c>
       <c r="G80" t="b">
         <v>1</v>
       </c>
       <c r="H80" t="b">
         <v>0</v>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FILATEX</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Filatex India Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3025,62 +3450,72 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>111.36</v>
+        <v>22.95</v>
       </c>
       <c r="E81" t="n">
-        <v>68.37</v>
+        <v>68.98</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2572</v>
+        <v>0.4437</v>
       </c>
       <c r="G81" t="b">
         <v>1</v>
       </c>
       <c r="H81" t="b">
         <v>0</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>DHAMPURSUG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>R R Kabel Limited</t>
+          <t>Dhampur Sugar Mills Limited</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2789.7</v>
+        <v>188.92</v>
       </c>
       <c r="E82" t="n">
-        <v>68.31</v>
+        <v>68.8</v>
       </c>
       <c r="F82" t="n">
-        <v>36.6381</v>
+        <v>2.334</v>
       </c>
       <c r="G82" t="b">
         <v>1</v>
       </c>
       <c r="H82" t="b">
         <v>0</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ARIHANTCAP</t>
+          <t>PANACHE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Arihant Capital Markets Limited</t>
+          <t>Panache Digilife Limited</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3089,62 +3524,72 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>94.13</v>
+        <v>569</v>
       </c>
       <c r="E83" t="n">
-        <v>68.28</v>
+        <v>68.78</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2935</v>
+        <v>2.4434</v>
       </c>
       <c r="G83" t="b">
         <v>1</v>
       </c>
       <c r="H83" t="b">
         <v>0</v>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GTECJAINX</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>G-TEC JAINX EDUCATION LIMITED</t>
+          <t>The Great Eastern Shipping Company Limited</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>36.19</v>
+        <v>1567.9</v>
       </c>
       <c r="E84" t="n">
-        <v>68.09</v>
+        <v>68.64</v>
       </c>
       <c r="F84" t="n">
-        <v>1.1449</v>
+        <v>4.8113</v>
       </c>
       <c r="G84" t="b">
         <v>1</v>
       </c>
       <c r="H84" t="b">
         <v>0</v>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LGHL</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Laxmi Goldorna House Limited</t>
+          <t>Gujarat Kidney And Super Speciality Limited</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3153,30 +3598,35 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>213.69</v>
+        <v>193.62</v>
       </c>
       <c r="E85" t="n">
-        <v>67.87</v>
+        <v>68.59</v>
       </c>
       <c r="F85" t="n">
-        <v>4.6214</v>
+        <v>0.6725</v>
       </c>
       <c r="G85" t="b">
         <v>1</v>
       </c>
       <c r="H85" t="b">
         <v>0</v>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LANDSMILL</t>
+          <t>SUNDROP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Landsmill Green Limited</t>
+          <t>Sundrop Brands Limited</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3185,30 +3635,35 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.93</v>
+        <v>746.8</v>
       </c>
       <c r="E86" t="n">
-        <v>67.86</v>
+        <v>68.59</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0551</v>
+        <v>3.6931</v>
       </c>
       <c r="G86" t="b">
         <v>1</v>
       </c>
       <c r="H86" t="b">
         <v>0</v>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>RPTECH</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BOSCH HOME COMFORT INDIA LIMITED</t>
+          <t>Rashi Peripherals Limited</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3217,62 +3672,72 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1976.9</v>
+        <v>958.25</v>
       </c>
       <c r="E87" t="n">
-        <v>67.78</v>
+        <v>68.45</v>
       </c>
       <c r="F87" t="n">
-        <v>23.3312</v>
+        <v>12.0136</v>
       </c>
       <c r="G87" t="b">
         <v>1</v>
       </c>
       <c r="H87" t="b">
         <v>0</v>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>WELSPUNLIV</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cello World Limited</t>
+          <t>Welspun Living Limited</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>369.15</v>
+        <v>235.86</v>
       </c>
       <c r="E88" t="n">
-        <v>67.65000000000001</v>
+        <v>68.39</v>
       </c>
       <c r="F88" t="n">
-        <v>3.9351</v>
+        <v>0.227</v>
       </c>
       <c r="G88" t="b">
         <v>1</v>
       </c>
       <c r="H88" t="b">
         <v>0</v>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ENGINERSIN</t>
+          <t>FILATEX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Engineers India Limited</t>
+          <t>Filatex India Limited</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3281,94 +3746,109 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>313.3</v>
+        <v>111.36</v>
       </c>
       <c r="E89" t="n">
-        <v>67.64</v>
+        <v>68.37</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.2572</v>
       </c>
       <c r="G89" t="b">
         <v>1</v>
       </c>
       <c r="H89" t="b">
         <v>0</v>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>E2E Networks Limited</t>
+          <t>Optiemus Infracom Limited</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>688.9</v>
+        <v>861.9</v>
       </c>
       <c r="E90" t="n">
-        <v>67.56999999999999</v>
+        <v>68.33</v>
       </c>
       <c r="F90" t="n">
-        <v>4.63</v>
+        <v>12.8041</v>
       </c>
       <c r="G90" t="b">
         <v>1</v>
       </c>
       <c r="H90" t="b">
         <v>0</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ADFFOODS</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ADF Foods Limited</t>
+          <t>LG Electronics India Limited</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>293.1</v>
+        <v>1780.3</v>
       </c>
       <c r="E91" t="n">
-        <v>67.5</v>
+        <v>68.22</v>
       </c>
       <c r="F91" t="n">
-        <v>2.7755</v>
+        <v>6.7304</v>
       </c>
       <c r="G91" t="b">
         <v>1</v>
       </c>
       <c r="H91" t="b">
         <v>0</v>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HMAAGRO</t>
+          <t>GTECJAINX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HMA Agro Industries Limited</t>
+          <t>G-TEC JAINX EDUCATION LIMITED</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3377,94 +3857,109 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>24.56</v>
+        <v>36.19</v>
       </c>
       <c r="E92" t="n">
-        <v>67.38</v>
+        <v>68.09</v>
       </c>
       <c r="F92" t="n">
-        <v>0.051</v>
+        <v>1.1449</v>
       </c>
       <c r="G92" t="b">
         <v>1</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CHEMPLASTS</t>
+          <t>EPACKPEB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chemplast Sanmar Limited</t>
+          <t>EPack Prefab Technologies Limited</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>210.24</v>
+        <v>267.44</v>
       </c>
       <c r="E93" t="n">
-        <v>67.17</v>
+        <v>68.05</v>
       </c>
       <c r="F93" t="n">
-        <v>2.2555</v>
+        <v>2.1051</v>
       </c>
       <c r="G93" t="b">
         <v>1</v>
       </c>
       <c r="H93" t="b">
         <v>0</v>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HALEOSLABS</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HALEOS LABS LIMITED</t>
+          <t>Dynamatic Technologies Limited</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1587.8</v>
+        <v>13723</v>
       </c>
       <c r="E94" t="n">
-        <v>66.98</v>
+        <v>67.91</v>
       </c>
       <c r="F94" t="n">
-        <v>8.260999999999999</v>
+        <v>108.8603</v>
       </c>
       <c r="G94" t="b">
         <v>1</v>
       </c>
       <c r="H94" t="b">
         <v>0</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>LGHL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Raymond Realty Limited</t>
+          <t>Laxmi Goldorna House Limited</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3473,30 +3968,35 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>707.8</v>
+        <v>213.69</v>
       </c>
       <c r="E95" t="n">
-        <v>66.98</v>
+        <v>67.87</v>
       </c>
       <c r="F95" t="n">
-        <v>6.9415</v>
+        <v>4.6214</v>
       </c>
       <c r="G95" t="b">
         <v>1</v>
       </c>
       <c r="H95" t="b">
         <v>0</v>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RUBYMILLS</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The Ruby Mills Limited</t>
+          <t>BOSCH HOME COMFORT INDIA LIMITED</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3505,158 +4005,183 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>512.8</v>
+        <v>1976.9</v>
       </c>
       <c r="E96" t="n">
-        <v>66.98</v>
+        <v>67.78</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1087</v>
+        <v>23.3312</v>
       </c>
       <c r="G96" t="b">
         <v>1</v>
       </c>
       <c r="H96" t="b">
         <v>0</v>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TRACXN</t>
+          <t>SYNCOMF</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tracxn Technologies Limited</t>
+          <t>Syncom Formulations (India) Limited</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>34.34</v>
+        <v>24.94</v>
       </c>
       <c r="E97" t="n">
-        <v>66.91</v>
+        <v>67.73</v>
       </c>
       <c r="F97" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.1724</v>
       </c>
       <c r="G97" t="b">
         <v>1</v>
       </c>
       <c r="H97" t="b">
         <v>0</v>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BATLIBOI</t>
+          <t>DELTACORP</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Batliboi Limited</t>
+          <t>Delta Corp Limited</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>96.16</v>
+        <v>82.37</v>
       </c>
       <c r="E98" t="n">
-        <v>66.77</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>1.0924</v>
+        <v>1.7591</v>
       </c>
       <c r="G98" t="b">
         <v>1</v>
       </c>
       <c r="H98" t="b">
         <v>0</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SANGAMIND</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sangam (India) Limited</t>
+          <t>Lemon Tree Hotels Limited</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>642.4</v>
+        <v>112.52</v>
       </c>
       <c r="E99" t="n">
-        <v>66.68000000000001</v>
+        <v>67.63</v>
       </c>
       <c r="F99" t="n">
-        <v>6.6129</v>
+        <v>0.8286</v>
       </c>
       <c r="G99" t="b">
         <v>1</v>
       </c>
       <c r="H99" t="b">
         <v>0</v>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jamna Auto Industries Limited</t>
+          <t>Black Box Limited</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>144.21</v>
+        <v>884.85</v>
       </c>
       <c r="E100" t="n">
-        <v>66.54000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F100" t="n">
-        <v>0.666</v>
+        <v>7.2173</v>
       </c>
       <c r="G100" t="b">
         <v>1</v>
       </c>
       <c r="H100" t="b">
         <v>0</v>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>E2E</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tega Industries Limited</t>
+          <t>E2E Networks Limited</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3665,30 +4190,35 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2092.5</v>
+        <v>688.9</v>
       </c>
       <c r="E101" t="n">
-        <v>66.38</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="F101" t="n">
-        <v>6.8734</v>
+        <v>4.63</v>
       </c>
       <c r="G101" t="b">
         <v>1</v>
       </c>
       <c r="H101" t="b">
         <v>0</v>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ADFFOODS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>ADF Foods Limited</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3697,30 +4227,35 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1081.15</v>
+        <v>293.1</v>
       </c>
       <c r="E102" t="n">
-        <v>66.29000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="F102" t="n">
-        <v>1.1411</v>
+        <v>2.7755</v>
       </c>
       <c r="G102" t="b">
         <v>1</v>
       </c>
       <c r="H102" t="b">
         <v>0</v>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>HMAAGRO</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LLOYDS ENGINEERING WORKS LIMITED</t>
+          <t>HMA Agro Industries Limited</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3729,30 +4264,35 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>101.15</v>
+        <v>24.56</v>
       </c>
       <c r="E103" t="n">
-        <v>66.05</v>
+        <v>67.38</v>
       </c>
       <c r="F103" t="n">
-        <v>1.531</v>
+        <v>0.051</v>
       </c>
       <c r="G103" t="b">
         <v>1</v>
       </c>
       <c r="H103" t="b">
         <v>0</v>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AGSTRA</t>
+          <t>CHEMPLASTS</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AGS Transact Technologies Limited</t>
+          <t>Chemplast Sanmar Limited</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3761,30 +4301,35 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2.45</v>
+        <v>210.24</v>
       </c>
       <c r="E104" t="n">
-        <v>65.90000000000001</v>
+        <v>67.17</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0456</v>
+        <v>2.2555</v>
       </c>
       <c r="G104" t="b">
         <v>1</v>
       </c>
       <c r="H104" t="b">
         <v>0</v>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>HALEOSLABS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Aarti Pharmalabs Limited</t>
+          <t>HALEOS LABS LIMITED</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3793,30 +4338,35 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>975</v>
+        <v>1587.8</v>
       </c>
       <c r="E105" t="n">
-        <v>65.84999999999999</v>
+        <v>66.98</v>
       </c>
       <c r="F105" t="n">
-        <v>5.8981</v>
+        <v>8.260999999999999</v>
       </c>
       <c r="G105" t="b">
         <v>1</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>RUBYMILLS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Quality Power Electrical Equipments Limited</t>
+          <t>The Ruby Mills Limited</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3825,62 +4375,72 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1648.8</v>
+        <v>512.8</v>
       </c>
       <c r="E106" t="n">
-        <v>65.61</v>
+        <v>66.98</v>
       </c>
       <c r="F106" t="n">
-        <v>5.9296</v>
+        <v>0.1087</v>
       </c>
       <c r="G106" t="b">
         <v>1</v>
       </c>
       <c r="H106" t="b">
         <v>0</v>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>GMBREW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>GM Breweries Limited</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>393.55</v>
+        <v>984.95</v>
       </c>
       <c r="E107" t="n">
-        <v>65.47</v>
+        <v>66.78</v>
       </c>
       <c r="F107" t="n">
-        <v>0.1212</v>
+        <v>1.1339</v>
       </c>
       <c r="G107" t="b">
         <v>1</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>BATLIBOI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jash Engineering Limited</t>
+          <t>Batliboi Limited</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3889,30 +4449,35 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>594.95</v>
+        <v>96.16</v>
       </c>
       <c r="E108" t="n">
-        <v>65.45999999999999</v>
+        <v>66.77</v>
       </c>
       <c r="F108" t="n">
-        <v>1.7545</v>
+        <v>1.0924</v>
       </c>
       <c r="G108" t="b">
         <v>1</v>
       </c>
       <c r="H108" t="b">
         <v>0</v>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>SANGAMIND</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Capillary Technologies India Limited</t>
+          <t>Sangam (India) Limited</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3921,62 +4486,72 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>587.2</v>
+        <v>642.4</v>
       </c>
       <c r="E109" t="n">
-        <v>65.42</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>6.5035</v>
+        <v>6.6129</v>
       </c>
       <c r="G109" t="b">
         <v>1</v>
       </c>
       <c r="H109" t="b">
         <v>0</v>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SAMBHV</t>
+          <t>SHADOWFAX</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sambhv Steel Tubes Limited</t>
+          <t>Shadowfax Technologies Limited</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>162.19</v>
+        <v>292.85</v>
       </c>
       <c r="E110" t="n">
-        <v>65.42</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>0.8438</v>
+        <v>1.1992</v>
       </c>
       <c r="G110" t="b">
         <v>1</v>
       </c>
       <c r="H110" t="b">
         <v>0</v>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Allied Blenders and Distillers Limited</t>
+          <t>Tega Industries Limited</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3985,62 +4560,72 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>714.65</v>
+        <v>2092.5</v>
       </c>
       <c r="E111" t="n">
-        <v>65.40000000000001</v>
+        <v>66.38</v>
       </c>
       <c r="F111" t="n">
-        <v>2.0038</v>
+        <v>6.8734</v>
       </c>
       <c r="G111" t="b">
         <v>1</v>
       </c>
       <c r="H111" t="b">
         <v>0</v>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>KRISHNADEF</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Limited</t>
+          <t>Krishna Defence And Allied Industries Limited</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>452</v>
+        <v>1242.1</v>
       </c>
       <c r="E112" t="n">
-        <v>65.37</v>
+        <v>66.31</v>
       </c>
       <c r="F112" t="n">
-        <v>1.7836</v>
+        <v>31.655</v>
       </c>
       <c r="G112" t="b">
         <v>1</v>
       </c>
       <c r="H112" t="b">
         <v>0</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AARNAV</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Limited</t>
+          <t>LLOYDS ENGINEERING WORKS LIMITED</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4049,30 +4634,35 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>37.01</v>
+        <v>101.1</v>
       </c>
       <c r="E113" t="n">
-        <v>65.29000000000001</v>
+        <v>65.94</v>
       </c>
       <c r="F113" t="n">
-        <v>0.3892</v>
+        <v>1.3078</v>
       </c>
       <c r="G113" t="b">
         <v>1</v>
       </c>
       <c r="H113" t="b">
         <v>0</v>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SMLT</t>
+          <t>AGSTRA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sarthak Metals Limited</t>
+          <t>AGS Transact Technologies Limited</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4081,62 +4671,72 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>74.06</v>
+        <v>2.45</v>
       </c>
       <c r="E114" t="n">
-        <v>65.11</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F114" t="n">
-        <v>2.1126</v>
+        <v>0.0456</v>
       </c>
       <c r="G114" t="b">
         <v>1</v>
       </c>
       <c r="H114" t="b">
         <v>0</v>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KABRAEXTRU</t>
+          <t>PROTEAN</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Limited</t>
+          <t>Protean eGov Technologies Limited</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>815.7</v>
+        <v>669.95</v>
       </c>
       <c r="E115" t="n">
-        <v>65.06999999999999</v>
+        <v>65.66</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6227</v>
+        <v>6.848</v>
       </c>
       <c r="G115" t="b">
         <v>1</v>
       </c>
       <c r="H115" t="b">
         <v>0</v>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Castrol India Limited</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4145,30 +4745,35 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>200.2</v>
+        <v>393.55</v>
       </c>
       <c r="E116" t="n">
-        <v>65.05</v>
+        <v>65.47</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3199</v>
+        <v>0.1212</v>
       </c>
       <c r="G116" t="b">
         <v>1</v>
       </c>
       <c r="H116" t="b">
         <v>0</v>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>JAYBARMARU</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Jay Bharat Maruti Limited</t>
+          <t>Jash Engineering Limited</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4177,30 +4782,35 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>134.37</v>
+        <v>594.95</v>
       </c>
       <c r="E117" t="n">
-        <v>64.67</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="F117" t="n">
-        <v>2.9318</v>
+        <v>1.7545</v>
       </c>
       <c r="G117" t="b">
         <v>1</v>
       </c>
       <c r="H117" t="b">
         <v>0</v>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>SAMBHV</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Isgec Heavy Engineering Limited</t>
+          <t>Sambhv Steel Tubes Limited</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4209,126 +4819,146 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>905</v>
+        <v>162.19</v>
       </c>
       <c r="E118" t="n">
-        <v>64.48999999999999</v>
+        <v>65.42</v>
       </c>
       <c r="F118" t="n">
-        <v>7.7341</v>
+        <v>0.8438</v>
       </c>
       <c r="G118" t="b">
         <v>1</v>
       </c>
       <c r="H118" t="b">
         <v>0</v>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>The Great Eastern Shipping Company Limited</t>
+          <t>Aditya Infotech Limited</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1532.6</v>
+        <v>4064.9</v>
       </c>
       <c r="E119" t="n">
-        <v>64.22</v>
+        <v>65.31</v>
       </c>
       <c r="F119" t="n">
-        <v>4.9504</v>
+        <v>34.3903</v>
       </c>
       <c r="G119" t="b">
         <v>1</v>
       </c>
       <c r="H119" t="b">
         <v>0</v>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHEKHAWATI</t>
+          <t>AARNAV</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shekhawati Industries Limited</t>
+          <t>Aarnav Fashions Limited</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>27.17</v>
+        <v>37.01</v>
       </c>
       <c r="E120" t="n">
-        <v>64.22</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>0.3624</v>
+        <v>0.3892</v>
       </c>
       <c r="G120" t="b">
         <v>1</v>
       </c>
       <c r="H120" t="b">
         <v>0</v>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>RAYMONDREL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Indiabulls Limited</t>
+          <t>Raymond Realty Limited</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>30.95</v>
+        <v>701.8</v>
       </c>
       <c r="E121" t="n">
-        <v>64.05</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F121" t="n">
-        <v>0.136</v>
+        <v>6.5594</v>
       </c>
       <c r="G121" t="b">
         <v>1</v>
       </c>
       <c r="H121" t="b">
         <v>0</v>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ANSALAPI</t>
+          <t>SMLT</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ansal Properties &amp; Infrastructure Limited</t>
+          <t>Sarthak Metals Limited</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4337,30 +4967,35 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3.92</v>
+        <v>74.06</v>
       </c>
       <c r="E122" t="n">
-        <v>63.77</v>
+        <v>65.11</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0243</v>
+        <v>2.1126</v>
       </c>
       <c r="G122" t="b">
         <v>1</v>
       </c>
       <c r="H122" t="b">
         <v>0</v>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TICL</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Twamev Construction and Infrastructure Limited</t>
+          <t>Kabra Extrusion Technik Limited</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4369,30 +5004,35 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>8.57</v>
+        <v>815.7</v>
       </c>
       <c r="E123" t="n">
-        <v>63.72</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>0.3863</v>
+        <v>0.6227</v>
       </c>
       <c r="G123" t="b">
         <v>1</v>
       </c>
       <c r="H123" t="b">
         <v>0</v>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SANATHAN</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sanathan Textiles Limited</t>
+          <t>Jay Bharat Maruti Limited</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4401,62 +5041,72 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>525.65</v>
+        <v>134.37</v>
       </c>
       <c r="E124" t="n">
-        <v>63.6</v>
+        <v>64.67</v>
       </c>
       <c r="F124" t="n">
-        <v>3.3622</v>
+        <v>2.9318</v>
       </c>
       <c r="G124" t="b">
         <v>1</v>
       </c>
       <c r="H124" t="b">
         <v>0</v>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PRIMO</t>
+          <t>ACE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Primo Chemicals Limited</t>
+          <t>Action Construction Equipment Limited</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>26.97</v>
+        <v>1249.9</v>
       </c>
       <c r="E125" t="n">
-        <v>63.59</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>0.4494</v>
+        <v>0.023</v>
       </c>
       <c r="G125" t="b">
         <v>1</v>
       </c>
       <c r="H125" t="b">
         <v>0</v>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EMKAY</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Emkay Global Financial Services Limited</t>
+          <t>Isgec Heavy Engineering Limited</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4465,30 +5115,35 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>285.6</v>
+        <v>905</v>
       </c>
       <c r="E126" t="n">
-        <v>63.54</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>2.2057</v>
+        <v>7.7341</v>
       </c>
       <c r="G126" t="b">
         <v>1</v>
       </c>
       <c r="H126" t="b">
         <v>0</v>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GVPIL</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GE Power India Limited</t>
+          <t>Shekhawati Industries Limited</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4497,30 +5152,35 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>734.85</v>
+        <v>27.17</v>
       </c>
       <c r="E127" t="n">
-        <v>63.42</v>
+        <v>64.22</v>
       </c>
       <c r="F127" t="n">
-        <v>9.748100000000001</v>
+        <v>0.3624</v>
       </c>
       <c r="G127" t="b">
         <v>1</v>
       </c>
       <c r="H127" t="b">
         <v>0</v>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TIMEX</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Timex Group India Limited</t>
+          <t>Indiabulls Limited</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4529,30 +5189,35 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>731.7</v>
+        <v>30.95</v>
       </c>
       <c r="E128" t="n">
-        <v>63.41</v>
+        <v>64.05</v>
       </c>
       <c r="F128" t="n">
-        <v>1.0644</v>
+        <v>0.136</v>
       </c>
       <c r="G128" t="b">
         <v>1</v>
       </c>
       <c r="H128" t="b">
         <v>0</v>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CAPTRUST</t>
+          <t>ANSALAPI</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Capital Trust Limited</t>
+          <t>Ansal Properties &amp; Infrastructure Limited</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4561,30 +5226,35 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>20.98</v>
+        <v>3.92</v>
       </c>
       <c r="E129" t="n">
-        <v>63.36</v>
+        <v>63.77</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1575</v>
+        <v>0.0243</v>
       </c>
       <c r="G129" t="b">
         <v>1</v>
       </c>
       <c r="H129" t="b">
         <v>0</v>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>TICL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Carborundum Universal Limited</t>
+          <t>Twamev Construction and Infrastructure Limited</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4593,62 +5263,72 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1269.6</v>
+        <v>8.57</v>
       </c>
       <c r="E130" t="n">
-        <v>62.93</v>
+        <v>63.72</v>
       </c>
       <c r="F130" t="n">
-        <v>8.956200000000001</v>
+        <v>0.3863</v>
       </c>
       <c r="G130" t="b">
         <v>1</v>
       </c>
       <c r="H130" t="b">
         <v>0</v>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BOROLTD</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Borosil Limited</t>
+          <t>SEDEMAC Mechatronics Limited</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>286.85</v>
+        <v>3425.6</v>
       </c>
       <c r="E131" t="n">
-        <v>62.79</v>
+        <v>63.63</v>
       </c>
       <c r="F131" t="n">
-        <v>2.0987</v>
+        <v>11.4479</v>
       </c>
       <c r="G131" t="b">
         <v>1</v>
       </c>
       <c r="H131" t="b">
         <v>0</v>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NGLFINE</t>
+          <t>SANATHAN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NGL Fine-Chem Limited</t>
+          <t>Sanathan Textiles Limited</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4657,30 +5337,35 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3122.1</v>
+        <v>525.65</v>
       </c>
       <c r="E132" t="n">
-        <v>62.76</v>
+        <v>63.6</v>
       </c>
       <c r="F132" t="n">
-        <v>43.4763</v>
+        <v>3.3622</v>
       </c>
       <c r="G132" t="b">
         <v>1</v>
       </c>
       <c r="H132" t="b">
         <v>0</v>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AHCL</t>
+          <t>PRIMO</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Anlon Healthcare Limited</t>
+          <t>Primo Chemicals Limited</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4689,30 +5374,35 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>29.66</v>
+        <v>26.97</v>
       </c>
       <c r="E133" t="n">
-        <v>62.54</v>
+        <v>63.59</v>
       </c>
       <c r="F133" t="n">
-        <v>0.2431</v>
+        <v>0.4494</v>
       </c>
       <c r="G133" t="b">
         <v>1</v>
       </c>
       <c r="H133" t="b">
         <v>0</v>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>EMKAY</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SEDEMAC Mechatronics Limited</t>
+          <t>Emkay Global Financial Services Limited</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4721,62 +5411,72 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3399.6</v>
+        <v>285.6</v>
       </c>
       <c r="E134" t="n">
-        <v>62.41</v>
+        <v>63.54</v>
       </c>
       <c r="F134" t="n">
-        <v>16.7372</v>
+        <v>2.2057</v>
       </c>
       <c r="G134" t="b">
         <v>1</v>
       </c>
       <c r="H134" t="b">
         <v>0</v>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SYNCOMF</t>
+          <t>TRACXN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Syncom Formulations (India) Limited</t>
+          <t>Tracxn Technologies Limited</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>23.22</v>
+        <v>33.89</v>
       </c>
       <c r="E135" t="n">
-        <v>62.29</v>
+        <v>63.45</v>
       </c>
       <c r="F135" t="n">
-        <v>0.2095</v>
+        <v>0.1163</v>
       </c>
       <c r="G135" t="b">
         <v>1</v>
       </c>
       <c r="H135" t="b">
         <v>0</v>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>GVPIL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Aditya Infotech Limited</t>
+          <t>GE Power India Limited</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4785,30 +5485,35 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3976</v>
+        <v>734.85</v>
       </c>
       <c r="E136" t="n">
-        <v>62.26</v>
+        <v>63.42</v>
       </c>
       <c r="F136" t="n">
-        <v>28.3265</v>
+        <v>9.748100000000001</v>
       </c>
       <c r="G136" t="b">
         <v>1</v>
       </c>
       <c r="H136" t="b">
         <v>0</v>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>CAPTRUST</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Vivimed Labs Limited</t>
+          <t>Capital Trust Limited</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4817,62 +5522,72 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6.28</v>
+        <v>20.98</v>
       </c>
       <c r="E137" t="n">
-        <v>61.86</v>
+        <v>63.36</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0426</v>
+        <v>0.1575</v>
       </c>
       <c r="G137" t="b">
         <v>1</v>
       </c>
       <c r="H137" t="b">
         <v>0</v>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>Bharat Heavy Electricals Limited</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>30.06</v>
+        <v>448.5</v>
       </c>
       <c r="E138" t="n">
-        <v>61.13</v>
+        <v>62.95</v>
       </c>
       <c r="F138" t="n">
-        <v>0.6096</v>
+        <v>2.7192</v>
       </c>
       <c r="G138" t="b">
         <v>1</v>
       </c>
       <c r="H138" t="b">
         <v>0</v>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MAXIND</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Max India Limited</t>
+          <t>Carborundum Universal Limited</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4881,30 +5596,35 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>165.84</v>
+        <v>1269.6</v>
       </c>
       <c r="E139" t="n">
-        <v>61.09</v>
+        <v>62.93</v>
       </c>
       <c r="F139" t="n">
-        <v>1.9166</v>
+        <v>8.956200000000001</v>
       </c>
       <c r="G139" t="b">
         <v>1</v>
       </c>
       <c r="H139" t="b">
         <v>0</v>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RAJTV</t>
+          <t>BOROLTD</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Raj Television Network Limited</t>
+          <t>Borosil Limited</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4913,30 +5633,35 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.72</v>
+        <v>286.85</v>
       </c>
       <c r="E140" t="n">
-        <v>61</v>
+        <v>62.79</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2334</v>
+        <v>2.0987</v>
       </c>
       <c r="G140" t="b">
         <v>1</v>
       </c>
       <c r="H140" t="b">
         <v>0</v>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GALAPREC</t>
+          <t>NGLFINE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Gala Precision Engineering Limited</t>
+          <t>NGL Fine-Chem Limited</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4945,62 +5670,72 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1161</v>
+        <v>3122.1</v>
       </c>
       <c r="E141" t="n">
-        <v>60.94</v>
+        <v>62.76</v>
       </c>
       <c r="F141" t="n">
-        <v>11.2704</v>
+        <v>43.4763</v>
       </c>
       <c r="G141" t="b">
         <v>1</v>
       </c>
       <c r="H141" t="b">
         <v>0</v>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DCI</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dc Infotech And Communication Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>343.05</v>
+        <v>1067.9</v>
       </c>
       <c r="E142" t="n">
-        <v>60.81</v>
+        <v>62.66</v>
       </c>
       <c r="F142" t="n">
-        <v>8.824</v>
+        <v>3.634</v>
       </c>
       <c r="G142" t="b">
         <v>1</v>
       </c>
       <c r="H142" t="b">
         <v>0</v>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>POWERICA</t>
+          <t>AHCL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Powerica Limited</t>
+          <t>Anlon Healthcare Limited</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5009,62 +5744,72 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>601.7</v>
+        <v>29.66</v>
       </c>
       <c r="E143" t="n">
-        <v>60.5</v>
+        <v>62.54</v>
       </c>
       <c r="F143" t="n">
-        <v>3.2958</v>
+        <v>0.2431</v>
       </c>
       <c r="G143" t="b">
         <v>1</v>
       </c>
       <c r="H143" t="b">
         <v>0</v>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>KRONOX</t>
+          <t>LANDSMILL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Kronox Lab Sciences Limited</t>
+          <t>Landsmill Green Limited</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>206.65</v>
+        <v>0.89</v>
       </c>
       <c r="E144" t="n">
-        <v>60.43</v>
+        <v>62.07</v>
       </c>
       <c r="F144" t="n">
-        <v>1.4741</v>
+        <v>0.0386</v>
       </c>
       <c r="G144" t="b">
         <v>1</v>
       </c>
       <c r="H144" t="b">
         <v>0</v>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>VIVIMEDLAB</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Greaves Cotton Limited</t>
+          <t>Vivimed Labs Limited</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5073,55 +5818,398 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>222.78</v>
+        <v>6.28</v>
       </c>
       <c r="E145" t="n">
-        <v>60.18</v>
+        <v>61.86</v>
       </c>
       <c r="F145" t="n">
-        <v>1.7182</v>
+        <v>0.0426</v>
       </c>
       <c r="G145" t="b">
         <v>1</v>
       </c>
       <c r="H145" t="b">
         <v>0</v>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>R R Kabel Limited</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>2722.5</v>
+      </c>
+      <c r="E146" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="F146" t="n">
+        <v>38.8451</v>
+      </c>
+      <c r="G146" t="b">
+        <v>1</v>
+      </c>
+      <c r="H146" t="b">
+        <v>0</v>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>QPOWER</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Quality Power Electrical Equipments Limited</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1615</v>
+      </c>
+      <c r="E147" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2.7843</v>
+      </c>
+      <c r="G147" t="b">
+        <v>1</v>
+      </c>
+      <c r="H147" t="b">
+        <v>0</v>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>HINDCON</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Hindcon Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="E148" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="G148" t="b">
+        <v>1</v>
+      </c>
+      <c r="H148" t="b">
+        <v>0</v>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>RAJTV</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Raj Television Network Limited</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="E149" t="n">
+        <v>61</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.2334</v>
+      </c>
+      <c r="G149" t="b">
+        <v>1</v>
+      </c>
+      <c r="H149" t="b">
+        <v>0</v>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>GALAPREC</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Gala Precision Engineering Limited</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E150" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="F150" t="n">
+        <v>11.2704</v>
+      </c>
+      <c r="G150" t="b">
+        <v>1</v>
+      </c>
+      <c r="H150" t="b">
+        <v>0</v>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>DCI</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Dc Infotech And Communication Limited</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>343.05</v>
+      </c>
+      <c r="E151" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="F151" t="n">
+        <v>8.824</v>
+      </c>
+      <c r="G151" t="b">
+        <v>1</v>
+      </c>
+      <c r="H151" t="b">
+        <v>0</v>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AARTIPHARM</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Aarti Pharmalabs Limited</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>953.35</v>
+      </c>
+      <c r="E152" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="F152" t="n">
+        <v>3.5936</v>
+      </c>
+      <c r="G152" t="b">
+        <v>1</v>
+      </c>
+      <c r="H152" t="b">
+        <v>0</v>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>KRONOX</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Limited</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>206.65</v>
+      </c>
+      <c r="E153" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1.4741</v>
+      </c>
+      <c r="G153" t="b">
+        <v>1</v>
+      </c>
+      <c r="H153" t="b">
+        <v>0</v>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>GREAVESCOT</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Greaves Cotton Limited</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>222.78</v>
+      </c>
+      <c r="E154" t="n">
+        <v>60.18</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.7182</v>
+      </c>
+      <c r="G154" t="b">
+        <v>1</v>
+      </c>
+      <c r="H154" t="b">
+        <v>0</v>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>RBZJEWEL</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>RBZ Jewellers Limited</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
         <v>196.15</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E155" t="n">
         <v>60.17</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F155" t="n">
         <v>1.0258</v>
       </c>
-      <c r="G146" t="b">
-        <v>1</v>
-      </c>
-      <c r="H146" t="b">
-        <v>0</v>
+      <c r="G155" t="b">
+        <v>1</v>
+      </c>
+      <c r="H155" t="b">
+        <v>0</v>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>Grey (Noise)</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H146"/>
+  <autoFilter ref="A1:I155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>